--- a/simscape-Formula-Student-Vehicle-Simscape_FS_25_2_4_10/formule_parameters.xlsx
+++ b/simscape-Formula-Student-Vehicle-Simscape_FS_25_2_4_10/formule_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ZCU\FS\simscape-Formula-Student-Vehicle-Simscape_FS_25_2_4_10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FS\simscape-Formula-Student-Vehicle-Simscape_FS_25_2_4_10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D1B30A-516F-4F5C-9143-816D3F5308CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B3A6A7-3549-429A-9823-6A63C7CA456A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4ECECE29-2178-4098-AF54-A809660206BF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4ECECE29-2178-4098-AF54-A809660206BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Chassis" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="157">
   <si>
     <t>kg</t>
   </si>
@@ -508,6 +508,12 @@
   </si>
   <si>
     <t>[2.85, -0.53, 0.17]</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Comments</t>
   </si>
 </sst>
 </file>
@@ -587,7 +593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -608,20 +614,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -957,16 +961,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B785261-18CD-499A-A2D8-C0AD178ED578}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15" style="7" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -980,7 +984,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -992,7 +996,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -1004,7 +1008,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -1018,7 +1022,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>82</v>
       </c>
@@ -1032,7 +1036,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>85</v>
       </c>
@@ -1046,7 +1050,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>88</v>
       </c>
@@ -1060,7 +1064,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>90</v>
       </c>
@@ -1074,7 +1078,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>92</v>
       </c>
@@ -1096,17 +1100,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D100CA5-3D5D-44A7-B4A9-C8A625038E4F}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -1117,10 +1121,10 @@
         <v>5</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1132,7 +1136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -1144,7 +1148,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1158,7 +1162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>55</v>
       </c>
@@ -1172,7 +1176,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>58</v>
       </c>
@@ -1186,7 +1190,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>61</v>
       </c>
@@ -1207,17 +1211,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEEF4AF1-BC7B-4E35-B508-E4B4DA39501A}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -1231,7 +1235,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1243,7 +1247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -1255,7 +1259,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -1269,7 +1273,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>115</v>
       </c>
@@ -1283,7 +1287,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>118</v>
       </c>
@@ -1297,7 +1301,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>121</v>
       </c>
@@ -1311,7 +1315,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>124</v>
       </c>
@@ -1325,7 +1329,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>127</v>
       </c>
@@ -1339,7 +1343,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>130</v>
       </c>
@@ -1353,7 +1357,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>133</v>
       </c>
@@ -1367,7 +1371,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>136</v>
       </c>
@@ -1381,7 +1385,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>139</v>
       </c>
@@ -1395,47 +1399,35 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1445,16 +1437,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627D45DE-1518-4088-B4C9-4504F1B3CC3B}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="17" style="7" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -1468,7 +1460,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1480,7 +1472,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -1492,7 +1484,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -1506,7 +1498,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>115</v>
       </c>
@@ -1520,7 +1512,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>118</v>
       </c>
@@ -1534,7 +1526,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>121</v>
       </c>
@@ -1548,7 +1540,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>124</v>
       </c>
@@ -1562,7 +1554,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>127</v>
       </c>
@@ -1576,7 +1568,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>147</v>
       </c>
@@ -1590,7 +1582,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>150</v>
       </c>
@@ -1604,7 +1596,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>136</v>
       </c>
@@ -1618,7 +1610,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>139</v>
       </c>
@@ -1632,67 +1624,67 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="6"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="6"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="6"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="6"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="6"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="6"/>
       <c r="C19" s="3"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="6"/>
       <c r="C20" s="3"/>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="6"/>
       <c r="C21" s="3"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="6"/>
       <c r="C22" s="3"/>
       <c r="D22" s="4"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="6"/>
       <c r="C23" s="3"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="6"/>
       <c r="C24" s="3"/>
@@ -1706,16 +1698,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02CEEB2-29CA-4A80-964B-0E83113805BE}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="17" style="7" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -1723,13 +1715,13 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>155</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1741,7 +1733,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -1753,7 +1745,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>51</v>
       </c>
@@ -1767,7 +1759,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>113</v>
       </c>
@@ -1789,15 +1781,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8B8937-B25F-4E8C-AC9D-A3CB8A1A3D1A}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.42578125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -1811,7 +1803,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1823,7 +1815,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -1835,7 +1827,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -1849,7 +1841,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
@@ -1863,7 +1855,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>104</v>
       </c>
@@ -1877,7 +1869,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>107</v>
       </c>
@@ -1891,7 +1883,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>110</v>
       </c>
@@ -1911,16 +1903,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B57B5F2-6481-424C-83F0-1F8B855E0EE2}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -1934,7 +1926,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1946,7 +1938,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -1958,7 +1950,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>42</v>
       </c>
@@ -1972,7 +1964,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>94</v>
       </c>
@@ -1986,7 +1978,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>97</v>
       </c>
@@ -2000,7 +1992,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>100</v>
       </c>
@@ -2022,16 +2014,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{750BC15A-EF8A-4B8C-BBDC-092384C717B6}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -2045,7 +2037,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -2057,7 +2049,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -2069,7 +2061,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>46</v>
       </c>
@@ -2083,7 +2075,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>64</v>
       </c>
@@ -2097,7 +2089,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>67</v>
       </c>
@@ -2111,7 +2103,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>70</v>
       </c>
@@ -2125,7 +2117,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>73</v>
       </c>
@@ -2139,7 +2131,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
@@ -2153,7 +2145,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>79</v>
       </c>
